--- a/artfynd/A 62522-2025 artfynd.xlsx
+++ b/artfynd/A 62522-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89596164</v>
+        <v>89596172</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436492.8585055428</v>
+        <v>436498</v>
       </c>
       <c r="R2" t="n">
-        <v>7012999.203112256</v>
+        <v>7012994</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89596162</v>
+        <v>89596164</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436500.9003599965</v>
+        <v>436493</v>
       </c>
       <c r="R3" t="n">
-        <v>7012994.987740258</v>
+        <v>7012999</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +849,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89596172</v>
+        <v>89596162</v>
       </c>
       <c r="B4" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436498.1753477972</v>
+        <v>436501</v>
       </c>
       <c r="R4" t="n">
-        <v>7012994.139894641</v>
+        <v>7012995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +950,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,11 +963,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 62522-2025 artfynd.xlsx
+++ b/artfynd/A 62522-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596172</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596164</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,8 +995,18 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596162</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>